--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C50189-8171-4585-B77C-635F10584AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF896C7-8C5D-4EEE-8BB7-60482CDA1BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3403,7 +3403,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -3582,13 +3582,13 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3787,7 +3787,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:BA59" totalsRowShown="0">
-  <autoFilter ref="A2:BA59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A2:BA59" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Infraestructura"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="53">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -4209,64 +4215,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="17" t="s">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="16" t="s">
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
+      <c r="AQ1" s="18"/>
+      <c r="AR1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="AS1" s="16"/>
-      <c r="AT1" s="16"/>
-      <c r="AU1" s="16"/>
-      <c r="AV1" s="16"/>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16"/>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16"/>
+      <c r="AS1" s="17"/>
+      <c r="AT1" s="17"/>
+      <c r="AU1" s="17"/>
+      <c r="AV1" s="17"/>
+      <c r="AW1" s="17"/>
+      <c r="AX1" s="17"/>
+      <c r="AY1" s="17"/>
+      <c r="AZ1" s="17"/>
     </row>
     <row r="2" spans="1:53" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4429,7 +4435,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="182.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
@@ -4573,7 +4579,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="69.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -4715,7 +4721,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="179.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="179.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2013000100022</v>
       </c>
@@ -4869,7 +4875,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="69.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>2013000100074</v>
       </c>
@@ -5176,7 +5182,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="102" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>107</v>
       </c>
@@ -5475,7 +5481,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="148.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>2017000100029</v>
       </c>
@@ -5629,7 +5635,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>129</v>
       </c>
@@ -5931,7 +5937,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="117.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>2020000020058</v>
       </c>
@@ -6238,7 +6244,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="164.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>2020000100644</v>
       </c>
@@ -6392,7 +6398,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="156.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>2020002700073</v>
       </c>
@@ -6696,7 +6702,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="152.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:53" ht="152.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>2021000100333</v>
       </c>
@@ -6850,7 +6856,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="19" spans="1:53" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:53" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>2021000100361</v>
       </c>
@@ -7004,7 +7010,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:53" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:53" ht="151.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>193</v>
       </c>
@@ -7158,7 +7164,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:53" ht="155.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>199</v>
       </c>
@@ -7608,7 +7614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="198" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:53" ht="198" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>219</v>
       </c>
@@ -7752,7 +7758,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:53" ht="117.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>228</v>
       </c>
@@ -8051,7 +8057,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:53" ht="127.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>2022000020011</v>
       </c>
@@ -8805,7 +8811,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:53" ht="69.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>2023002700076</v>
       </c>
@@ -9105,7 +9111,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:53" ht="114" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>287</v>
       </c>
@@ -9402,7 +9408,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:53" ht="100.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>2023002700150</v>
       </c>
@@ -9709,7 +9715,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:53" ht="104.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>2023002700175</v>
       </c>
@@ -10007,7 +10013,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:53" ht="119.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>2024002700066</v>
       </c>
@@ -10161,7 +10167,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:53" ht="69.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>2024002700151</v>
       </c>
@@ -10313,7 +10319,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:53" ht="148.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>2024002700174</v>
       </c>
@@ -10464,7 +10470,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:53" ht="90.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>2024002700176</v>
       </c>
@@ -10918,7 +10924,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:53" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:53" ht="121.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>2024002700184</v>
       </c>
@@ -11069,7 +11075,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="47" spans="1:53" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:53" ht="127.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
         <v>2024702150036</v>
       </c>
@@ -11342,7 +11348,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="49" spans="1:53" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:53" ht="69.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>2025000020019</v>
       </c>
@@ -12089,7 +12095,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="54" spans="1:53" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:53" ht="69.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>2025002700023</v>
       </c>
@@ -12243,7 +12249,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="55" spans="1:53" ht="117" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:53" ht="117" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>2025002700025</v>
       </c>
@@ -13001,54 +13007,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="17" t="s">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="16" t="s">
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="AJ1" s="16"/>
-      <c r="AK1" s="16"/>
-      <c r="AL1" s="16"/>
-      <c r="AM1" s="16"/>
-      <c r="AN1" s="16"/>
-      <c r="AO1" s="16"/>
-      <c r="AP1" s="16"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17"/>
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
     </row>
     <row r="2" spans="1:42" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -13283,7 +13289,7 @@
         <v>75</v>
       </c>
       <c r="AM3" s="4" t="str">
-        <f t="shared" ref="AM3:AM18" si="5">IFERROR(IF($G3="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($X3),ISNUMBER($Z3),$X3&lt;$Z3),0,IF($AH3&gt;=1,(IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))*$AL3/100,IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))),IF($G3="CONTRATADO SIN ACTA DE INICIO",IF(AND($Z3-$V3&gt;=0,$Z3-$V3&lt;=30),100,0),"")),"")</f>
+        <f t="shared" ref="AM3:AM17" si="5">IFERROR(IF($G3="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($X3),ISNUMBER($Z3),$X3&lt;$Z3),0,IF($AH3&gt;=1,(IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))*$AL3/100,IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))),IF($G3="CONTRATADO SIN ACTA DE INICIO",IF(AND($Z3-$V3&gt;=0,$Z3-$V3&lt;=30),100,0),"")),"")</f>
         <v/>
       </c>
       <c r="AN3" s="5">
@@ -14572,7 +14578,7 @@
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AM14" s="18">
+      <c r="AM14" s="16">
         <f t="shared" si="5"/>
         <v>58.04347826086957</v>
       </c>
@@ -14810,7 +14816,7 @@
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AM16" s="18">
+      <c r="AM16" s="16">
         <f t="shared" si="5"/>
         <v>76.521739130434781</v>
       </c>
@@ -14928,7 +14934,7 @@
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AM17" s="18">
+      <c r="AM17" s="16">
         <f t="shared" si="5"/>
         <v>74.782608695652186</v>
       </c>
@@ -15071,27 +15077,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
     </row>
     <row r="2" spans="1:19" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -20887,67 +20893,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="17" t="s">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="17"/>
-      <c r="AU1" s="16" t="s">
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
+      <c r="AO1" s="18"/>
+      <c r="AP1" s="18"/>
+      <c r="AQ1" s="18"/>
+      <c r="AR1" s="18"/>
+      <c r="AS1" s="18"/>
+      <c r="AT1" s="18"/>
+      <c r="AU1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="AV1" s="16"/>
-      <c r="AW1" s="16"/>
-      <c r="AX1" s="16"/>
-      <c r="AY1" s="16"/>
-      <c r="AZ1" s="16"/>
-      <c r="BA1" s="16"/>
-      <c r="BB1" s="16"/>
-      <c r="BC1" s="16"/>
+      <c r="AV1" s="17"/>
+      <c r="AW1" s="17"/>
+      <c r="AX1" s="17"/>
+      <c r="AY1" s="17"/>
+      <c r="AZ1" s="17"/>
+      <c r="BA1" s="17"/>
+      <c r="BB1" s="17"/>
+      <c r="BC1" s="17"/>
     </row>
     <row r="2" spans="1:56" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -30081,13 +30087,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EC8A490-CD83-40CA-A212-F25B98C4FB54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9116407A-27D8-4391-8933-4B5FFA647364}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC75C9C4-D5D7-4942-A144-DEC81B2583FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05796178-6D3D-4633-97C4-B73007695C11}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{337058F7-9E24-49F9-8623-E345A9FD39FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4AF643F-B038-4102-B001-4B66F6D477EE}"/>
 </file>